--- a/results/SanityStatus.xlsx
+++ b/results/SanityStatus.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Case ID</t>
   </si>
@@ -27,25 +27,16 @@
   <si>
     <t>Platform</t>
   </si>
-  <si>
-    <t>C72554</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Web</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -973,7 +964,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultColWidth="9.13888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -990,20 +981,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
